--- a/Participants/4_Shared_Toolkit/GBF_Consulting_Toolkit.xlsx
+++ b/Participants/4_Shared_Toolkit/GBF_Consulting_Toolkit.xlsx
@@ -15,7 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version Control" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding Scenarios" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Submission Checklist" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Request Log" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Submission Checklist" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -523,7 +524,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Workstream</t>
+          <t>Workflow</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -638,7 +639,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Read handbook, data room index and workstream briefs</t>
+          <t>Read handbook, index and workflow briefs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -822,7 +823,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>WS-A Lead</t>
+          <t>WF-A Lead</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -928,7 +929,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Confirm WS-A / WS-B pairs and audit process</t>
+          <t>Confirm A/B protocol and Request Log owners</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1043,98 +1044,98 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>File Analysis Request R-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>WF-A Lead</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Analysis_Request</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Team drive</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>W2-02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Profile all eight dataset tables (DB-1)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>WS-B Lead</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>WF-B Lead</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Profiling notes</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Team drive</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>W2-02</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>21 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Submit data quality report</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>WS-B Lead</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>B1 Data quality</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1149,12 +1150,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>22 Jul 2026</t>
+          <t>21 Jul 2026</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1164,22 +1165,22 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Submit interview synthesis</t>
+          <t>Submit data quality report (B internal)</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Research Lead</t>
+          <t>WF-B Lead</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>A2 Synthesis</t>
+          <t>B1 Data quality</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1222,921 +1223,1675 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
+          <t>Submit interview synthesis</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Research Lead</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>A2 Synthesis</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>W2-05</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>22 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
           <t>Submit empathy and journey maps</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>WS-A Lead</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>WF-A Lead</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>A3 Maps</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>Buddy + drive</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>W2-06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>23 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Return Findings Memo FM-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>WF-B Lead</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Findings_Memo</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Team drive</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>W2-07</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>24 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Submit dashboard version 1 (B working file)</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>WF-B Lead</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>B2 Dashboard</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Check-in 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>W3-01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>27 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>File Analysis Requests R-02 and R-03</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>WF-A Lead</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Analysis_Request</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Team drive</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>W3-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>28 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Return FM-02 and FM-03; analysis summary</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>WF-B Lead</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>B3 + Findings</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Excel+PDF</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>W3-03</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>30 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Submit strategic options (cite Request IDs)</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>WF-A Lead</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>A4 Options</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>W3-04</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Submit evidence-check memo on options</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>WF-B Lead</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>B4 Evidence check</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Team drive</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Check-in 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>W4-01</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Submit validation protocol and trade-off reflection</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Research / WF-A</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>A5 A6</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>W4-02</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>06 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Submit funding scenarios (DB-5)</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Ops Analyst</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>B5 Funding</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>W4-03</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>06 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Submit recommendation revision log</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Engagement Lead</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>A7 Revision log</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Team drive</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>W4-04</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Submit executive summary (draft)</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Engagement Lead</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Executive summary</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Check-in 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>W5-01</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>11 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Submit final report (draft for handoff)</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Engagement Lead</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Final report</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>W5-02</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>12 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Submit signed Cross-Workflow Handoff Checklist</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>PM Lead</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Handoff checklist</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Buddy</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>W5-03</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>13 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>BOARD PRESENTATION</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Board deck</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Present live</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>PPTX</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Check-in 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>W5-04</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Submit all final deliverables</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>PM Lead</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>All finals</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Programme portal</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>PDF+PPTX+Excel</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>W6-01</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>17 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Submit peer evaluation (individual, confidential)</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Each member</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Peer evaluation</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>W6-02</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>18 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Submit reflection journal (individual)</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Each member</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Reflection</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Final Submission Checklist - due Friday 14 August 2026, 17:00 ICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Deliverable</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Submitted?</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>File name</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Project Charter</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RACI matrix</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Information credibility matrix</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Issue tree (A1)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Stakeholder map (A1b)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Analysis Requests (min. 3)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data quality report (B1)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Findings Memos (min. 3)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Interview synthesis (A2)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Empathy and journey maps (A3)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dashboard (B2)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Analysis summary (B3)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Strategic options (A4)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W2-05</t>
+          <t>Evidence-check memo (B4)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23 Jul 2026</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>WS-A audit of data quality report</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Trade-off reflection (A5)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>WS-A auditor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Audit memo</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Team drive</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>W2-06</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>24 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Submit dashboard version 1</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Validation protocol (A6)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Funding scenarios (B5)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>WS-B Lead</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>B2 Dashboard</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>Check-in 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>W3-01</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>28 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Submit dashboard v2 and analysis summary</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>WS-B Lead</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>B3 Analysis</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Excel+PDF</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>W3-02</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>30 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Submit strategic options (draft)</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>WS-A Lead</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>A4 Options</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Revision log (A7)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>W3-03</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>31 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Submit evidence-check memo on options</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>WS-B Lead</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>B4 Evidence check</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Team drive</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Executive summary</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Check-in 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>W4-01</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>05 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Submit completed validation protocol</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Final report</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Research Lead</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>A6 Validation</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>W4-02</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>06 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Submit funding scenarios (DB-5)</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Ops Analyst</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>B5 Funding</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>W4-03</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>06 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Submit recommendation revision log</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Board deck</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Engagement Lead</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>A7 Revision log</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Team drive</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PPTX + PDF</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Handoff checklist (signed)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>W4-04</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>07 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Submit executive summary (draft)</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Engagement Lead</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Executive summary</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Peer evaluation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Check-in 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>W5-01</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>11 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Submit final report (draft for audit)</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Engagement Lead</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Final report</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Reflection journal</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>W5-02</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>12 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Submit signed cross-workstream audit checklist</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>PM Lead</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Audit checklist</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>Buddy</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>W5-03</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>13 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>BOARD PRESENTATION</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Board deck</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Present live</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>PPTX</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Check-in 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>W5-04</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>14 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Submit all final deliverables</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>PM Lead</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>All finals</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Programme portal</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>PDF+PPTX+Excel</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>W6-01</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>17 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Submit peer evaluation (individual, confidential)</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Individual</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Each member</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Peer evaluation</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>W6-02</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>18 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Submit reflection journal (individual)</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Individual</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Each member</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Reflection</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2155,7 +2910,7 @@
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2193,7 +2948,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Workstream (A / B / All)</t>
+          <t>Workflow (A / B / All)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2418,7 +3173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2452,12 +3207,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>WS-A Lead</t>
+          <t>WF-A Lead</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>WS-B Lead</t>
+          <t>WF-B Lead</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2553,7 +3308,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data quality report (B1)</t>
+          <t>Analysis Requests (A)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2563,14 +3318,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>R</t>
@@ -2578,7 +3333,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2590,12 +3345,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dashboard (B2)</t>
+          <t>Findings Memos (B)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2627,7 +3382,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Interview synthesis (A2)</t>
+          <t>Data quality report (B1)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2637,12 +3392,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>A/R</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>I</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2664,98 +3419,98 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Strategic options (A4)</t>
+          <t>Dashboard (B2)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Validation protocol (A6)</t>
+          <t>Interview synthesis (A2)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Funding scenarios (B5)</t>
+          <t>Strategic options (A4)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>R</t>
@@ -2768,51 +3523,51 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Final report</t>
+          <t>Trade-off reflection (A5)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Board deck</t>
+          <t>Validation protocol (A6)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2849,35 +3604,146 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cross-workstream audit</t>
+          <t>Funding scenarios (B5)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Final report</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Board deck</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cross-workflow handoff</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -3193,7 +4059,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Use audited unit costs from D-12 and VPBank terms from D-03. State every assumption. Workstream B owns this tab.</t>
+          <t>Use audited unit costs from D-12 and VPBank terms from D-03. State every assumption. Workflow B owns this tab.</t>
         </is>
       </c>
     </row>
@@ -3349,560 +4215,223 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Final Submission Checklist - due Friday 14 August 2026, 17:00 ICT</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Deliverable</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Workstream</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Submitted?</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>File name</t>
-        </is>
-      </c>
-    </row>
+          <t>Analysis Request Log - minimum three completed R/FM pairs before final options</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Workflow A files requests. Workflow B returns Findings Memos. Engagement Lead reviews weekly. Do not share the raw dataset with A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Project Charter</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Request ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Date filed</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Filed by (A)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Decision question (short)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Findings Memo ID</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Date returned</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Returned by (B)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RACI matrix</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FM-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Information credibility matrix</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FM-02</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Issue tree (A1)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>R-03</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FM-03</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Stakeholder map (A1b)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>R-04</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FM-04</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data quality report (B1)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>R-05</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FM-05</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Interview synthesis (A2)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>FM-06</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Empathy and journey maps (A3)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>R-07</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FM-07</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dashboard (B2)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Analysis summary (B3)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Strategic options (A4)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Evidence-check memo (B4)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Validation protocol (A6)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Funding scenarios (B5)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Revision log (A7)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Executive summary</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>4-5</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Final report</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Board deck</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>PPTX + PDF</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Audit checklist (signed)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Peer evaluation</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Individual</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Reflection journal</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Individual</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+          <t>R-08</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FM-08</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Participants/4_Shared_Toolkit/GBF_Consulting_Toolkit.xlsx
+++ b/Participants/4_Shared_Toolkit/GBF_Consulting_Toolkit.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Programme start: Monday 13 July 2026. All deadlines 17:00 Indochina Time (ICT) unless noted.</t>
+          <t>Programme opens Sunday 26 July 2026; working weeks Mon-Fri from Monday 27 July. Closes Sunday 20 September 2026. All deadlines 17:00 ICT unless noted.</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13 Jul 2026</t>
+          <t>27 Jul 2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13 Jul 2026</t>
+          <t>27 Jul 2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Read handbook, index and workflow briefs</t>
+          <t>Read guideline, index and workflow briefs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -682,12 +682,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>14 Jul 2026</t>
+          <t>29 Jul 2026</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Submit signed Project Charter</t>
+          <t>Submit Project Charter (online confirm)</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>14 Jul 2026</t>
+          <t>29 Jul 2026</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -786,303 +786,303 @@
       <c r="L8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>W1-05</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>15 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Confirm A/B protocol and Request Log owners</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Engagement Lead</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Buddy</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Check-in 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>W1-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Update Master Timeline with named owners</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PM Lead</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>This workbook</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>W2-01</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Submit problem statement and issue tree</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>WF-A Lead</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>A1 Issue tree</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Buddy + drive</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>W1-06</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>16 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>W2-02</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>06 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Submit stakeholder map</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Research Lead</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>A1b Stakeholder</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>W2-03</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>06 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Submit information credibility matrix</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Research Lead</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Credibility matrix</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>Buddy + drive</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>W1-07</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>17 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Confirm A/B protocol and Request Log owners</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Engagement Lead</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Buddy</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Check-in 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>W1-08</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>17 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Update Master Timeline with named owners</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PM Lead</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>This workbook</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>W2-01</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>20 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>File Analysis Request R-01</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>WF-A Lead</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Analysis_Request</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Team drive</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W2-02</t>
+          <t>W2-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1092,302 +1092,306 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20 Jul 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Buddy check-in: source interrogation habits</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Engagement Lead</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Buddy</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Check-in 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>W3-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>File Analysis Request R-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>WF-A Lead</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Analysis_Request</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Team drive</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>W3-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Profile all eight dataset tables (DB-1)</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>WF-B Lead</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Profiling notes</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Team drive</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>W2-03</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>21 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Submit data quality report (B internal)</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>WF-B Lead</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>B1 Data quality</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>W2-04</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>22 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Submit interview synthesis</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Research Lead</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>A2 Synthesis</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>W2-05</t>
+          <t>W3-03</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 3</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>22 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Submit data quality report (B internal)</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>WF-B Lead</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>B1 Data quality</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>W3-04</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>12 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Submit empathy and journey maps</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Submit interview synthesis</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>WF-A Lead</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>A3 Maps</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Research Lead</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>A2 Synthesis</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Buddy + drive</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>W2-06</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>23 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Return Findings Memo FM-01</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>WF-B Lead</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Findings_Memo</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Team drive</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>W2-07</t>
+          <t>W3-05</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Week 3</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>24 Jul 2026</t>
+          <t>12 Aug 2026</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1397,22 +1401,22 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Submit dashboard version 1 (B working file)</t>
+          <t>Submit empathy and journey maps</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>WF-B Lead</t>
+          <t>WF-A Lead</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>B2 Dashboard</t>
+          <t>A3 Maps</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1422,19 +1426,15 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Check-in 2</t>
-        </is>
-      </c>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W3-01</t>
+          <t>W3-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1444,233 +1444,233 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>27 Jul 2026</t>
+          <t>13 Aug 2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Return Findings Memo FM-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>WF-B Lead</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Findings_Memo</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Team drive</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>W3-07</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Submit dashboard version 1 (B working file)</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>WF-B Lead</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>B2 Dashboard</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Check-in 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>W4-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>17 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>File Analysis Requests R-02 and R-03</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>WF-A Lead</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Analysis_Request</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Team drive</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>W3-02</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>28 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>W4-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>18 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Return FM-02 and FM-03; analysis summary</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>WF-B Lead</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>B3 + Findings</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Buddy + drive</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Excel+PDF</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>W3-03</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>30 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Submit strategic options (cite Request IDs)</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>WF-A Lead</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>A4 Options</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>W3-04</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>31 Jul 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Submit evidence-check memo on options</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>WF-B Lead</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>B4 Evidence check</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Team drive</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Check-in 3</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>W4-01</t>
+          <t>W4-03</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Submit validation protocol and trade-off reflection</t>
+          <t>Submit strategic options (cite Request IDs)</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Research / WF-A</t>
+          <t>WF-A Lead</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>A5 A6</t>
+          <t>A4 Options</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1728,7 +1728,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>W4-02</t>
+          <t>W4-04</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>06 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Submit funding scenarios (DB-5)</t>
+          <t>Submit evidence-check memo on options</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -1763,45 +1763,49 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Ops Analyst</t>
+          <t>WF-B Lead</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>B5 Funding</t>
+          <t>B4 Evidence check</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Buddy + drive</t>
+          <t>Team drive</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr"/>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Check-in 4</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>W4-03</t>
+          <t>W5-01</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Week 4</t>
+          <t>Week 5</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>06 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1811,27 +1815,27 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Submit recommendation revision log</t>
+          <t>Submit validation protocol and trade-off reflection</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Engagement Lead</t>
+          <t>Research / WF-A</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>A7 Revision log</t>
+          <t>A5 A6</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Team drive</t>
+          <t>Buddy + drive</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -1844,22 +1848,22 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>W4-04</t>
+          <t>W5-02</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Week 4</t>
+          <t>Week 5</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>27 Aug 2026</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1869,22 +1873,22 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Submit executive summary (draft)</t>
+          <t>Submit funding scenarios (DB-5)</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Engagement Lead</t>
+          <t>Ops Analyst</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Executive summary</t>
+          <t>B5 Funding</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1894,19 +1898,15 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>Check-in 4</t>
-        </is>
-      </c>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>W5-01</t>
+          <t>W5-03</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>27 Aug 2026</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Submit final report (draft for handoff)</t>
+          <t>Submit recommendation revision log</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Final report</t>
+          <t>A7 Revision log</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Buddy + drive</t>
+          <t>Team drive</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -1964,7 +1964,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>W5-02</t>
+          <t>W5-04</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1974,42 +1974,42 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>12 Aug 2026</t>
+          <t>28 Aug 2026</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Submit signed Cross-Workflow Handoff Checklist</t>
+          <t>Submit executive summary (draft)</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>PM Lead</t>
+          <t>Engagement Lead</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Handoff checklist</t>
+          <t>Executive summary</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Buddy</t>
+          <t>Buddy + drive</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -2017,37 +2017,41 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Check-in 5</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>W5-03</t>
+          <t>W6-01</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Week 5</t>
+          <t>Week 6</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>13 Aug 2026</t>
+          <t>01 Sep 2026</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>BOARD PRESENTATION</t>
+          <t>Submit final report (draft for handoff)</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2057,203 +2061,381 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
+          <t>Engagement Lead</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Final report</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>W6-02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>02 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Confirm Cross-Workflow Handoff Checklist (online)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Board deck</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Present live</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>PPTX</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Check-in 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>W5-04</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>14 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PM Lead</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Handoff checklist</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Buddy</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>W6-03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Submit all final deliverables</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Buddy check-in: board rehearsal plan</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>PM Lead</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>All finals</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Programme portal</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>PDF+PPTX+Excel</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>W6-01</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>17 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Submit peer evaluation (individual, confidential)</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Individual</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Each member</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>Peer evaluation</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Engagement Lead</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Buddy</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Check-in 6</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>W6-02</t>
+          <t>W7-01</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Week 6</t>
+          <t>Week 7</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>18 Aug 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>BOARD PRESENTATION</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Board deck</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Present live</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>PPTX</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>Check-in 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>W7-02</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>11 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Submit all final deliverables</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>PM Lead</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>All finals</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Programme portal</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>PDF+PPTX+Excel</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>W8-01</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Submit peer evaluation (individual, confidential)</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Each member</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Peer evaluation</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>W8-02</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>Submit reflection journal (individual)</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>Individual</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>Each member</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>Reflection</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2280,7 +2462,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Final Submission Checklist - due Friday 14 August 2026, 17:00 ICT</t>
+          <t>Final Submission Checklist - due Friday 11 September 2026, 17:00 ICT</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2565,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -2407,7 +2589,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -2431,7 +2613,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -2455,7 +2637,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -2479,7 +2661,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -2503,7 +2685,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -2527,7 +2709,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -2551,7 +2733,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -2575,7 +2757,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -2599,7 +2781,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -2623,7 +2805,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -2647,7 +2829,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -2671,7 +2853,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -2695,7 +2877,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -2719,7 +2901,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -2743,7 +2925,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -2767,7 +2949,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -2791,7 +2973,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -2815,7 +2997,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -2824,7 +3006,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Handoff checklist (signed)</t>
+          <t>Handoff checklist (confirmed)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2839,7 +3021,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -2863,7 +3045,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -2887,7 +3069,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>

--- a/Participants/4_Shared_Toolkit/GBF_Consulting_Toolkit.xlsx
+++ b/Participants/4_Shared_Toolkit/GBF_Consulting_Toolkit.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Buddy check-in: source interrogation habits</t>
+          <t>Buddy check-in: source interrogation; B Data Estate Brief draft status</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1142,120 +1142,120 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>W3-01</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Week 3</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>10 Aug 2026</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>File Analysis Request R-01</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Submit Data Estate Brief (catalog only - no raw file)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>WF-B Lead</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Data_Estate_Brief</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Team drive</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>W3-02</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>11 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Submit Demand Brief (ranked decision needs after reading DEB)</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>WF-A Lead</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Analysis_Request</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Demand_Brief</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Team drive</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>W3-02</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>10 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Profile all eight dataset tables (DB-1)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>WF-B Lead</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Profiling notes</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Team drive</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Submit data quality report (B internal)</t>
+          <t>Submit Analysis Plan for priority Demand items</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>B1 Data quality</t>
+          <t>Analysis_Plan</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Buddy + drive</t>
+          <t>Team drive</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1328,166 +1328,166 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>11 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Submit data quality report (B internal)</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>WF-B Lead</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>B1 Data quality</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>W3-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>12 Aug 2026</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>File Analysis Request R-01 (aligned to Demand + Plan)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>WF-A Lead</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Analysis_Request</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Team drive</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>W3-06</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>12 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Submit interview synthesis</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Research Lead</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>A2 Synthesis</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Buddy + drive</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>W3-05</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>12 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Submit empathy and journey maps</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>WF-A Lead</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>A3 Maps</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>W3-06</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>13 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Return Findings Memo FM-01</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>WF-B Lead</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Findings_Memo</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Team drive</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>14 Aug 2026</t>
+          <t>12 Aug 2026</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1517,22 +1517,22 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Submit dashboard version 1 (B working file)</t>
+          <t>Submit empathy and journey maps</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>WF-B Lead</t>
+          <t>WF-A Lead</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>B2 Dashboard</t>
+          <t>A3 Maps</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1542,270 +1542,266 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Check-in 3</t>
-        </is>
-      </c>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>W3-08</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>13 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Return Findings Memo FM-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>WF-B Lead</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Findings_Memo</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Team drive</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>W3-09</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Submit dashboard version 1 (B working file)</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>WF-B Lead</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>B2 Dashboard</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Check-in 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>W4-01</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Week 4</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>17 Aug 2026</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>File Analysis Requests R-02 and R-03</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>File Analysis Requests R-02 and R-03 (with Plan updates)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>WF-A Lead</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Analysis_Request</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Team drive</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>W4-02</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Week 4</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>18 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Return FM-02 and FM-03; analysis summary</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Return FM-02 and FM-03; submit B3 analysis summary</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>WF-B Lead</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>B3 + Findings</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Buddy + drive</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Excel+PDF</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>W4-03</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>20 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Submit strategic options (cite Request IDs)</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>WF-A Lead</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>A4 Options</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Buddy + drive</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>W4-04</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>21 Aug 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Submit evidence-check memo on options</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>WF-B Lead</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>B4 Evidence check</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Team drive</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Check-in 4</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>W5-01</t>
+          <t>W4-03</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Week 5</t>
+          <t>Week 4</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1815,7 +1811,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Submit validation protocol and trade-off reflection</t>
+          <t>Submit strategic options (cite Request IDs)</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1825,12 +1821,12 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Research / WF-A</t>
+          <t>WF-A Lead</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>A5 A6</t>
+          <t>A4 Options</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1848,22 +1844,22 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>W5-02</t>
+          <t>W4-04</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Week 5</t>
+          <t>Week 4</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>27 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1873,7 +1869,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Submit funding scenarios (DB-5)</t>
+          <t>Submit evidence-check memo on options</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -1883,30 +1879,34 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Ops Analyst</t>
+          <t>WF-B Lead</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>B5 Funding</t>
+          <t>B4 Evidence check</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>Buddy + drive</t>
+          <t>Team drive</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr"/>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Check-in 4</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>W5-03</t>
+          <t>W5-01</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>27 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1931,27 +1931,27 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Submit recommendation revision log</t>
+          <t>Submit validation protocol and trade-off reflection</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Engagement Lead</t>
+          <t>Research / WF-A</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>A7 Revision log</t>
+          <t>A5 A6</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Team drive</t>
+          <t>Buddy + drive</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -1964,7 +1964,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>W5-04</t>
+          <t>W5-02</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>28 Aug 2026</t>
+          <t>27 Aug 2026</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1989,22 +1989,22 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Submit executive summary (draft)</t>
+          <t>Submit funding scenarios (DB-5)</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Engagement Lead</t>
+          <t>Ops Analyst</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Executive summary</t>
+          <t>B5 Funding</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2014,428 +2014,544 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Check-in 5</t>
-        </is>
-      </c>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t>W5-03</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>27 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Submit recommendation revision log</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Engagement Lead</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>A7 Revision log</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Team drive</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>W5-04</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>28 Aug 2026</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Submit executive summary (draft)</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Engagement Lead</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Executive summary</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Buddy + drive</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Check-in 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>W6-01</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Week 6</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>01 Sep 2026</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>Submit final report (draft for handoff)</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>Engagement Lead</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>Final report</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>Buddy + drive</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>W6-02</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Week 6</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>02 Sep 2026</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Confirm Cross-Workflow Handoff Checklist (online)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Confirm Cross-Workflow Handoff Checklist online (copy Templates/Cross_Workflow_Handoff_Checklist.docx; tick + typed name/date; export PDF)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>PM Lead</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Handoff checklist</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Buddy</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="L33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>W6-03</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Week 6</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>04 Sep 2026</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Buddy check-in: board rehearsal plan</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Engagement Lead</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Buddy</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Check-in 6</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>W7-01</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>10 Sep 2026</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>BOARD PRESENTATION</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Board deck</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>Present live</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>PPTX</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Check-in 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>W7-02</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>11 Sep 2026</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Submit all final deliverables</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>PM Lead</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>All finals</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>Programme portal</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>PDF+PPTX+Excel</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>W8-01</t>
+          <t>W7-01</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Week 8</t>
+          <t>Week 7</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Submit peer evaluation (individual, confidential)</t>
+          <t>BOARD PRESENTATION</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Each member</t>
+          <t>All</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Peer evaluation</t>
+          <t>Board deck</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Present live</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr"/>
+          <t>PPTX</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Check-in 7</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
+          <t>W7-02</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>11 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Submit all final deliverables</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>PM Lead</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>All finals</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Programme portal</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>PDF+PPTX+Excel</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>W8-01</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Submit peer evaluation (individual, confidential)</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Each member</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Peer evaluation</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
           <t>W8-02</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Week 8</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>15 Sep 2026</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>Submit reflection journal (individual)</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>Individual</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>Each member</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>Reflection</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="L36" s="4" t="inlineStr"/>
+      <c r="L38" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2448,12 +2564,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -2646,7 +2762,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data quality report (B1)</t>
+          <t>Data Estate Brief</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2670,12 +2786,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Findings Memos (min. 3)</t>
+          <t>Demand Brief</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2685,7 +2801,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -2694,12 +2810,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Interview synthesis (A2)</t>
+          <t>Analysis Plans</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2709,7 +2825,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -2718,12 +2834,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Empathy and journey maps (A3)</t>
+          <t>Data quality report (B1)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2742,7 +2858,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dashboard (B2)</t>
+          <t>Findings Memos (min. 3)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2752,12 +2868,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -2766,12 +2882,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analysis summary (B3)</t>
+          <t>Interview synthesis (A2)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2781,7 +2897,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -2790,7 +2906,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Strategic options (A4)</t>
+          <t>Empathy and journey maps (A3)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2805,7 +2921,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -2814,7 +2930,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Evidence-check memo (B4)</t>
+          <t>Dashboard (B2)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2824,12 +2940,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -2838,12 +2954,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Trade-off reflection (A5)</t>
+          <t>Analysis summary (B3)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2853,7 +2969,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -2862,12 +2978,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Validation protocol (A6)</t>
+          <t>Strategic options (A4)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2877,7 +2993,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -2886,7 +3002,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Funding scenarios (B5)</t>
+          <t>Evidence-check memo (B4)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2896,12 +3012,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -2910,12 +3026,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Revision log (A7)</t>
+          <t>Trade-off reflection (A5)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2934,7 +3050,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Executive summary</t>
+          <t>Validation protocol (A6)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2949,7 +3065,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -2958,22 +3074,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Final report</t>
+          <t>Funding scenarios (B5)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6-7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -2982,7 +3098,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Board deck</t>
+          <t>Revision log (A7)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2992,12 +3108,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PPTX + PDF</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -3006,7 +3122,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Handoff checklist (confirmed)</t>
+          <t>Executive summary</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3021,7 +3137,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -3030,12 +3146,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Peer evaluation</t>
+          <t>Final report</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>All</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3045,7 +3161,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -3054,26 +3170,98 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Reflection journal</t>
+          <t>Board deck</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>All</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>PPTX + PDF</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Handoff checklist (confirmed online)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PDF from Templates/Cross_Workflow_Handoff_Checklist.docx</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Peer evaluation</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Reflection journal</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3355,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3490,7 +3678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analysis Requests (A)</t>
+          <t>Data Estate Brief (B)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3500,14 +3688,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>A/R</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>R</t>
@@ -3515,7 +3703,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3527,7 +3715,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Findings Memos (B)</t>
+          <t>Demand Brief (A)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3537,14 +3725,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>R</t>
@@ -3552,7 +3740,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3564,7 +3752,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data quality report (B1)</t>
+          <t>Analysis Plans (B)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3601,32 +3789,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dashboard (B2)</t>
+          <t>Analysis Requests (A)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>I</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>R</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3638,7 +3826,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Interview synthesis (A2)</t>
+          <t>Findings Memos (B)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3648,12 +3836,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>A/R</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>I</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3675,61 +3863,61 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Strategic options (A4)</t>
+          <t>Data quality report (B1)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trade-off reflection (A5)</t>
+          <t>Dashboard (B2)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>R</t>
@@ -3737,7 +3925,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3749,61 +3937,61 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Validation protocol (A6)</t>
+          <t>Interview synthesis (A2)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Funding scenarios (B5)</t>
+          <t>Strategic options (A4)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>R</t>
@@ -3816,51 +4004,51 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Final report</t>
+          <t>Trade-off reflection (A5)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Board deck</t>
+          <t>Validation protocol (A6)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3897,35 +4085,146 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Funding scenarios (B5)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Final report</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Board deck</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Cross-workflow handoff</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -4220,15 +4519,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4241,7 +4542,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Use audited unit costs from D-12 and VPBank terms from D-03. State every assumption. Workflow B owns this tab.</t>
+          <t>Use audited unit costs from D-12, VPBank terms from D-03, and hub_capacity_jan2026. Choose scenarios that fit GBF's mission and Board ambition without breaking staff, mentor or finance capacity. State every assumption. Workflow B owns this tab.</t>
         </is>
       </c>
     </row>
@@ -4286,101 +4587,133 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Current annual completers (approx.)</t>
+          <t>Youth served (guideline / registry)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2104</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Broad placement rate (D-01 definition)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
+          <t>D-01 2024 completers (public report)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>592</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Broad placement rate (D-01 definition)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Formal placement rate (ST-02)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>63%</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capacity check source</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>hub_capacity_jan2026 + hub_costs_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Growth in completers</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Est. total cost (VND)</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Funding gap</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Can meet 65% honestly?</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Staff/mentor headroom OK?</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Fits mission + Board?</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Key risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Hold steady</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Moderate growth</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>+30%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Hold steady</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Moderate growth</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>+30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Aggressive growth</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>+80%</t>
         </is>
@@ -4397,32 +4730,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Analysis Request Log - minimum three completed R/FM pairs before final options</t>
+          <t>A↔B Evidence Log - Estate → Demand → Plan → R/FM (min. three R/FM before options)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Workflow A files requests. Workflow B returns Findings Memos. Engagement Lead reviews weekly. Do not share the raw dataset with A.</t>
+          <t>Sequence: B files Data Estate Brief; A files Demand Brief; B files Analysis Plan; A files R-xx; B returns FM-xx. Engagement Lead reviews weekly. Do not share the raw dataset or data dictionary with A - catalog only in the Estate Brief.</t>
         </is>
       </c>
     </row>
@@ -4450,30 +4785,40 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>Linked Demand rank</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Analysis Plan ID</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>Urgency</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Findings Memo ID</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Date returned</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Returned by (B)</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -4487,10 +4832,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>AP-01</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>FM-01</t>
         </is>
@@ -4504,10 +4854,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>AP-02</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>FM-02</t>
         </is>
@@ -4521,10 +4876,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>AP-03</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>FM-03</t>
         </is>
@@ -4538,10 +4898,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>AP-04</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>FM-04</t>
         </is>
@@ -4555,10 +4920,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>AP-05</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>FM-05</t>
         </is>
@@ -4572,10 +4942,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>AP-06</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>FM-06</t>
         </is>
@@ -4589,10 +4964,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>AP-07</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>FM-07</t>
         </is>
@@ -4606,14 +4986,51 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>AP-08</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>FM-08</t>
         </is>
       </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Loop milestones (tick when PDF is in A_B_Exchange/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Estate Brief (DEB-01) filed by B:</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Demand Brief (DMD-01) filed by A:</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>First Analysis Plan (AP-01) filed by B:</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
